--- a/msds-source/output/DY#2-WH029 EAGON WHITE 반광 MSDS.xlsx
+++ b/msds-source/output/DY#2-WH029 EAGON WHITE 반광 MSDS.xlsx
@@ -1505,11 +1505,15 @@
     <row r="45" ht="33.75" customHeight="1" s="59">
       <c r="A45" s="77" t="inlineStr">
         <is>
+          <t>폴리에스테르 경화제</t>
+        </is>
+      </c>
+      <c r="B45" s="78" t="n"/>
+      <c r="C45" s="79" t="inlineStr">
+        <is>
           <t>N,N,N',N'-Tetrakis(2-hydroxyethyl)adipamide</t>
         </is>
       </c>
-      <c r="B45" s="78" t="n"/>
-      <c r="C45" s="79" t="n"/>
       <c r="D45" s="79" t="inlineStr">
         <is>
           <t>6334-25-4</t>
@@ -3754,7 +3758,7 @@
     <row r="262" ht="15.75" customHeight="1" s="59">
       <c r="A262" s="70" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 N,N,N',N'-Tetrakis(2-hydroxyethyl)adipamide</t>
+          <t xml:space="preserve">                 폴리에스테르 경화제</t>
         </is>
       </c>
       <c r="B262" s="89" t="inlineStr">
@@ -3798,7 +3802,7 @@
     <row r="266" ht="18" customHeight="1" s="59">
       <c r="A266" s="70" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 N,N,N',N'-Tetrakis(2-hydroxyethyl)adipamide</t>
+          <t xml:space="preserve">                 폴리에스테르 경화제</t>
         </is>
       </c>
       <c r="B266" s="89" t="inlineStr">
@@ -3862,7 +3866,7 @@
     <row r="272" ht="17.25" customHeight="1" s="59">
       <c r="A272" s="70" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 N,N,N',N'-Tetrakis(2-hydroxyethyl)adipamide</t>
+          <t xml:space="preserve">                 폴리에스테르 경화제</t>
         </is>
       </c>
       <c r="B272" s="89" t="inlineStr">
@@ -4625,365 +4629,365 @@
     </row>
   </sheetData>
   <mergeCells count="359">
-    <mergeCell ref="B146:E146"/>
-    <mergeCell ref="B217:E217"/>
-    <mergeCell ref="A337:E337"/>
     <mergeCell ref="B300:E300"/>
-    <mergeCell ref="B65:E65"/>
-    <mergeCell ref="B192:E192"/>
+    <mergeCell ref="B74:E74"/>
     <mergeCell ref="A51:B51"/>
-    <mergeCell ref="B74:E74"/>
     <mergeCell ref="B201:E201"/>
     <mergeCell ref="B68:E68"/>
     <mergeCell ref="B139:E139"/>
     <mergeCell ref="B310:E310"/>
-    <mergeCell ref="A339:E339"/>
-    <mergeCell ref="B123:E123"/>
     <mergeCell ref="B76:E76"/>
-    <mergeCell ref="B221:E221"/>
     <mergeCell ref="B203:E203"/>
-    <mergeCell ref="B110:E110"/>
     <mergeCell ref="B232:E232"/>
-    <mergeCell ref="B141:E141"/>
-    <mergeCell ref="A300:A302"/>
     <mergeCell ref="B326:E326"/>
     <mergeCell ref="B215:E215"/>
-    <mergeCell ref="A57:E57"/>
-    <mergeCell ref="B12:E12"/>
     <mergeCell ref="A247:E247"/>
     <mergeCell ref="B263:E263"/>
-    <mergeCell ref="B248:E248"/>
-    <mergeCell ref="B297:E297"/>
-    <mergeCell ref="B235:E235"/>
     <mergeCell ref="B244:E244"/>
     <mergeCell ref="B229:E229"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="B136:E136"/>
-    <mergeCell ref="B312:E312"/>
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B290:E290"/>
-    <mergeCell ref="B299:E299"/>
-    <mergeCell ref="B13:E13"/>
     <mergeCell ref="B69:E69"/>
-    <mergeCell ref="B78:E78"/>
-    <mergeCell ref="B249:E249"/>
-    <mergeCell ref="B205:E205"/>
+    <mergeCell ref="B112:E112"/>
     <mergeCell ref="B87:E87"/>
-    <mergeCell ref="B112:E112"/>
-    <mergeCell ref="B243:E243"/>
-    <mergeCell ref="B314:E314"/>
     <mergeCell ref="B283:E283"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A83:E83"/>
     <mergeCell ref="B298:E298"/>
     <mergeCell ref="B64:E64"/>
     <mergeCell ref="A132:E132"/>
-    <mergeCell ref="A334:E334"/>
-    <mergeCell ref="B154:E154"/>
     <mergeCell ref="B237:E237"/>
     <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B129:E129"/>
     <mergeCell ref="B138:E138"/>
     <mergeCell ref="B309:E309"/>
-    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B209:E209"/>
     <mergeCell ref="A133:E133"/>
-    <mergeCell ref="B16:E16"/>
     <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B209:E209"/>
     <mergeCell ref="B301:E301"/>
-    <mergeCell ref="B131:E131"/>
     <mergeCell ref="B311:E311"/>
     <mergeCell ref="B140:E140"/>
+    <mergeCell ref="B18:E18"/>
     <mergeCell ref="B238:E238"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B223:E223"/>
-    <mergeCell ref="B220:E220"/>
     <mergeCell ref="B303:E303"/>
     <mergeCell ref="B77:E77"/>
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="B253:E253"/>
-    <mergeCell ref="C338:E338"/>
-    <mergeCell ref="B195:E195"/>
-    <mergeCell ref="B231:E231"/>
-    <mergeCell ref="B287:E287"/>
-    <mergeCell ref="B262:E262"/>
     <mergeCell ref="B240:E240"/>
-    <mergeCell ref="A4:E4"/>
     <mergeCell ref="A52:B52"/>
     <mergeCell ref="A280:E280"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="C340:E340"/>
-    <mergeCell ref="B289:E289"/>
     <mergeCell ref="B29:E29"/>
     <mergeCell ref="B329:E329"/>
     <mergeCell ref="B158:E158"/>
+    <mergeCell ref="A49:B49"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A49:B49"/>
     <mergeCell ref="B316:E316"/>
-    <mergeCell ref="A60:A63"/>
     <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B313:E313"/>
-    <mergeCell ref="B142:E142"/>
-    <mergeCell ref="B80:E80"/>
     <mergeCell ref="B95:E95"/>
     <mergeCell ref="B89:E89"/>
     <mergeCell ref="B160:E160"/>
     <mergeCell ref="B331:E331"/>
-    <mergeCell ref="B79:E79"/>
     <mergeCell ref="B306:E306"/>
-    <mergeCell ref="B144:E144"/>
-    <mergeCell ref="B315:E315"/>
-    <mergeCell ref="B242:E242"/>
     <mergeCell ref="B153:E153"/>
     <mergeCell ref="B224:E224"/>
-    <mergeCell ref="B302:E302"/>
-    <mergeCell ref="A84:E84"/>
-    <mergeCell ref="B252:E252"/>
-    <mergeCell ref="B81:E81"/>
-    <mergeCell ref="B208:E208"/>
     <mergeCell ref="A55:B55"/>
     <mergeCell ref="B184:E184"/>
-    <mergeCell ref="A42:E42"/>
     <mergeCell ref="B228:E228"/>
-    <mergeCell ref="B210:E210"/>
-    <mergeCell ref="B318:E318"/>
     <mergeCell ref="B17:E17"/>
     <mergeCell ref="B148:E148"/>
     <mergeCell ref="A72:E72"/>
-    <mergeCell ref="B157:E157"/>
     <mergeCell ref="B250:E250"/>
-    <mergeCell ref="A297:A299"/>
-    <mergeCell ref="B234:E234"/>
-    <mergeCell ref="B34:E34"/>
     <mergeCell ref="B317:E317"/>
-    <mergeCell ref="A338:B338"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="B270:E270"/>
-    <mergeCell ref="B99:E99"/>
-    <mergeCell ref="B172:E172"/>
     <mergeCell ref="B304:E304"/>
-    <mergeCell ref="B257:E257"/>
-    <mergeCell ref="B239:E239"/>
     <mergeCell ref="B254:E254"/>
     <mergeCell ref="B143:E143"/>
-    <mergeCell ref="B92:E92"/>
     <mergeCell ref="B319:E319"/>
-    <mergeCell ref="A340:B340"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="A291:E291"/>
     <mergeCell ref="B256:E256"/>
     <mergeCell ref="B85:E85"/>
-    <mergeCell ref="C341:E341"/>
-    <mergeCell ref="B94:E94"/>
     <mergeCell ref="A41:E41"/>
     <mergeCell ref="A95:A96"/>
     <mergeCell ref="A99:A104"/>
-    <mergeCell ref="B321:E321"/>
-    <mergeCell ref="B150:E150"/>
-    <mergeCell ref="B125:E125"/>
     <mergeCell ref="B159:E159"/>
     <mergeCell ref="A56:E56"/>
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="A32:A33"/>
     <mergeCell ref="A285:E285"/>
     <mergeCell ref="B96:E96"/>
-    <mergeCell ref="B323:E323"/>
     <mergeCell ref="B167:E167"/>
-    <mergeCell ref="B152:E152"/>
     <mergeCell ref="B272:E272"/>
     <mergeCell ref="B332:E332"/>
     <mergeCell ref="B259:E259"/>
     <mergeCell ref="B111:E111"/>
-    <mergeCell ref="B145:E145"/>
-    <mergeCell ref="B181:E181"/>
     <mergeCell ref="B274:E274"/>
     <mergeCell ref="B225:E225"/>
     <mergeCell ref="B175:E175"/>
+    <mergeCell ref="B267:E267"/>
+    <mergeCell ref="A295:E295"/>
+    <mergeCell ref="B269:E269"/>
+    <mergeCell ref="B325:E325"/>
+    <mergeCell ref="B91:E91"/>
+    <mergeCell ref="B327:E327"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B193:E193"/>
+    <mergeCell ref="B93:E93"/>
+    <mergeCell ref="B320:E320"/>
+    <mergeCell ref="B149:E149"/>
+    <mergeCell ref="B264:E264"/>
+    <mergeCell ref="B86:E86"/>
+    <mergeCell ref="B151:E151"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="A156:E156"/>
+    <mergeCell ref="B182:E182"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="A155:E155"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B211:E211"/>
+    <mergeCell ref="A284:E284"/>
+    <mergeCell ref="B183:E183"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="B177:E177"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B104:E104"/>
+    <mergeCell ref="B275:E275"/>
+    <mergeCell ref="B164:E164"/>
+    <mergeCell ref="B114:E114"/>
+    <mergeCell ref="B212:E212"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B206:E206"/>
+    <mergeCell ref="B106:E106"/>
+    <mergeCell ref="B277:E277"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A246:E246"/>
+    <mergeCell ref="B66:E66"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="B130:E130"/>
+    <mergeCell ref="B117:E117"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="B328:E328"/>
+    <mergeCell ref="A342:B342"/>
+    <mergeCell ref="B119:E119"/>
+    <mergeCell ref="A170:E170"/>
+    <mergeCell ref="B196:E196"/>
+    <mergeCell ref="B186:E186"/>
+    <mergeCell ref="B288:E288"/>
+    <mergeCell ref="B127:E127"/>
+    <mergeCell ref="B265:E265"/>
+    <mergeCell ref="B185:E185"/>
+    <mergeCell ref="A294:E294"/>
+    <mergeCell ref="B122:E122"/>
+    <mergeCell ref="B105:E105"/>
+    <mergeCell ref="B276:E276"/>
+    <mergeCell ref="B214:E214"/>
+    <mergeCell ref="B176:E176"/>
+    <mergeCell ref="B120:E120"/>
+    <mergeCell ref="B278:E278"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B171:E171"/>
+    <mergeCell ref="A67:A68"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="A107:E107"/>
+    <mergeCell ref="B204:E204"/>
+    <mergeCell ref="B198:E198"/>
+    <mergeCell ref="B296:E296"/>
+    <mergeCell ref="B75:E75"/>
+    <mergeCell ref="B135:E135"/>
+    <mergeCell ref="B233:E233"/>
+    <mergeCell ref="B62:E62"/>
+    <mergeCell ref="B227:E227"/>
+    <mergeCell ref="B202:E202"/>
+    <mergeCell ref="B199:E199"/>
+    <mergeCell ref="B70:E70"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="B293:E293"/>
+    <mergeCell ref="B322:E322"/>
+    <mergeCell ref="A333:E333"/>
+    <mergeCell ref="B88:E88"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="B82:E82"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A344:E344"/>
+    <mergeCell ref="B128:E128"/>
+    <mergeCell ref="B146:E146"/>
+    <mergeCell ref="B217:E217"/>
+    <mergeCell ref="A337:E337"/>
+    <mergeCell ref="B65:E65"/>
+    <mergeCell ref="B192:E192"/>
+    <mergeCell ref="A339:E339"/>
+    <mergeCell ref="B123:E123"/>
+    <mergeCell ref="B221:E221"/>
+    <mergeCell ref="B110:E110"/>
+    <mergeCell ref="B141:E141"/>
+    <mergeCell ref="A300:A302"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="B248:E248"/>
+    <mergeCell ref="B297:E297"/>
+    <mergeCell ref="B235:E235"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="B136:E136"/>
+    <mergeCell ref="B312:E312"/>
+    <mergeCell ref="B299:E299"/>
+    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="B78:E78"/>
+    <mergeCell ref="B249:E249"/>
+    <mergeCell ref="B205:E205"/>
+    <mergeCell ref="B243:E243"/>
+    <mergeCell ref="B314:E314"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A83:E83"/>
+    <mergeCell ref="A334:E334"/>
+    <mergeCell ref="B154:E154"/>
+    <mergeCell ref="B129:E129"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B131:E131"/>
+    <mergeCell ref="B223:E223"/>
+    <mergeCell ref="B220:E220"/>
+    <mergeCell ref="B195:E195"/>
+    <mergeCell ref="C338:E338"/>
+    <mergeCell ref="B231:E231"/>
+    <mergeCell ref="B287:E287"/>
+    <mergeCell ref="B262:E262"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="C340:E340"/>
+    <mergeCell ref="B289:E289"/>
+    <mergeCell ref="A60:A63"/>
+    <mergeCell ref="B313:E313"/>
+    <mergeCell ref="B142:E142"/>
+    <mergeCell ref="B80:E80"/>
+    <mergeCell ref="B79:E79"/>
+    <mergeCell ref="B144:E144"/>
+    <mergeCell ref="B315:E315"/>
+    <mergeCell ref="B242:E242"/>
+    <mergeCell ref="B302:E302"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="B252:E252"/>
+    <mergeCell ref="B81:E81"/>
+    <mergeCell ref="B208:E208"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="B210:E210"/>
+    <mergeCell ref="B318:E318"/>
+    <mergeCell ref="B157:E157"/>
+    <mergeCell ref="A297:A299"/>
+    <mergeCell ref="B234:E234"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B172:E172"/>
+    <mergeCell ref="A338:B338"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="B270:E270"/>
+    <mergeCell ref="B99:E99"/>
+    <mergeCell ref="B257:E257"/>
+    <mergeCell ref="B239:E239"/>
+    <mergeCell ref="B92:E92"/>
+    <mergeCell ref="A340:B340"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="A291:E291"/>
+    <mergeCell ref="C341:E341"/>
+    <mergeCell ref="B94:E94"/>
+    <mergeCell ref="B321:E321"/>
+    <mergeCell ref="B150:E150"/>
+    <mergeCell ref="B125:E125"/>
+    <mergeCell ref="B323:E323"/>
+    <mergeCell ref="B152:E152"/>
+    <mergeCell ref="B145:E145"/>
+    <mergeCell ref="B181:E181"/>
     <mergeCell ref="B258:E258"/>
     <mergeCell ref="B147:E147"/>
-    <mergeCell ref="B267:E267"/>
     <mergeCell ref="B245:E245"/>
-    <mergeCell ref="A295:E295"/>
     <mergeCell ref="B260:E260"/>
     <mergeCell ref="A279:E279"/>
-    <mergeCell ref="B269:E269"/>
     <mergeCell ref="A105:A106"/>
     <mergeCell ref="B207:E207"/>
-    <mergeCell ref="B325:E325"/>
     <mergeCell ref="B36:E36"/>
     <mergeCell ref="B163:E163"/>
     <mergeCell ref="A54:B54"/>
     <mergeCell ref="B113:E113"/>
     <mergeCell ref="B173:E173"/>
-    <mergeCell ref="B137:E137"/>
-    <mergeCell ref="B91:E91"/>
     <mergeCell ref="B271:E271"/>
     <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B327:E327"/>
     <mergeCell ref="B165:E165"/>
+    <mergeCell ref="B115:E115"/>
     <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B115:E115"/>
     <mergeCell ref="A341:B341"/>
-    <mergeCell ref="B320:E320"/>
-    <mergeCell ref="B93:E93"/>
-    <mergeCell ref="B149:E149"/>
-    <mergeCell ref="B264:E264"/>
     <mergeCell ref="B273:E273"/>
     <mergeCell ref="B102:E102"/>
-    <mergeCell ref="B86:E86"/>
+    <mergeCell ref="A71:E71"/>
     <mergeCell ref="C342:E342"/>
-    <mergeCell ref="A71:E71"/>
     <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B151:E151"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="A156:E156"/>
     <mergeCell ref="A336:E336"/>
-    <mergeCell ref="B182:E182"/>
-    <mergeCell ref="B38:E38"/>
     <mergeCell ref="B191:E191"/>
-    <mergeCell ref="A155:E155"/>
     <mergeCell ref="B178:E178"/>
-    <mergeCell ref="B40:E40"/>
     <mergeCell ref="B255:E255"/>
-    <mergeCell ref="B211:E211"/>
     <mergeCell ref="B226:E226"/>
-    <mergeCell ref="A284:E284"/>
-    <mergeCell ref="B183:E183"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="B177:E177"/>
     <mergeCell ref="B266:E266"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B104:E104"/>
-    <mergeCell ref="B275:E275"/>
-    <mergeCell ref="B164:E164"/>
     <mergeCell ref="B222:E222"/>
     <mergeCell ref="A85:A93"/>
+    <mergeCell ref="B32:E32"/>
     <mergeCell ref="B63:E63"/>
     <mergeCell ref="B197:E197"/>
     <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B212:E212"/>
-    <mergeCell ref="B32:E32"/>
     <mergeCell ref="B268:E268"/>
     <mergeCell ref="B324:E324"/>
-    <mergeCell ref="B35:E35"/>
     <mergeCell ref="B330:E330"/>
-    <mergeCell ref="B206:E206"/>
-    <mergeCell ref="B106:E106"/>
+    <mergeCell ref="B286:E286"/>
     <mergeCell ref="B308:E308"/>
-    <mergeCell ref="B286:E286"/>
-    <mergeCell ref="B277:E277"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A246:E246"/>
     <mergeCell ref="B261:E261"/>
     <mergeCell ref="B90:E90"/>
-    <mergeCell ref="B66:E66"/>
-    <mergeCell ref="A27:A30"/>
     <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B130:E130"/>
     <mergeCell ref="A5:E5"/>
-    <mergeCell ref="B117:E117"/>
-    <mergeCell ref="A14:E14"/>
     <mergeCell ref="A97:E97"/>
-    <mergeCell ref="B67:E67"/>
     <mergeCell ref="B179:E179"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="B328:E328"/>
-    <mergeCell ref="A342:B342"/>
     <mergeCell ref="B166:E166"/>
-    <mergeCell ref="B119:E119"/>
     <mergeCell ref="A161:E161"/>
-    <mergeCell ref="B114:E114"/>
     <mergeCell ref="B116:E116"/>
-    <mergeCell ref="A170:E170"/>
     <mergeCell ref="A77:A80"/>
     <mergeCell ref="B103:E103"/>
+    <mergeCell ref="B37:E37"/>
     <mergeCell ref="B174:E174"/>
-    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B230:E230"/>
     <mergeCell ref="B168:E168"/>
-    <mergeCell ref="B196:E196"/>
-    <mergeCell ref="B230:E230"/>
-    <mergeCell ref="B288:E288"/>
-    <mergeCell ref="B186:E186"/>
     <mergeCell ref="B118:E118"/>
-    <mergeCell ref="B127:E127"/>
     <mergeCell ref="B281:E281"/>
-    <mergeCell ref="B265:E265"/>
     <mergeCell ref="B169:E169"/>
     <mergeCell ref="A108:E108"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="A64:A66"/>
-    <mergeCell ref="B185:E185"/>
+    <mergeCell ref="B200:E200"/>
     <mergeCell ref="B134:E134"/>
     <mergeCell ref="B194:E194"/>
-    <mergeCell ref="B200:E200"/>
     <mergeCell ref="B292:E292"/>
     <mergeCell ref="B121:E121"/>
-    <mergeCell ref="A294:E294"/>
-    <mergeCell ref="B193:E193"/>
-    <mergeCell ref="B122:E122"/>
-    <mergeCell ref="B214:E214"/>
-    <mergeCell ref="B105:E105"/>
-    <mergeCell ref="B276:E276"/>
-    <mergeCell ref="B176:E176"/>
+    <mergeCell ref="B236:E236"/>
     <mergeCell ref="B307:E307"/>
-    <mergeCell ref="B236:E236"/>
     <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B120:E120"/>
-    <mergeCell ref="B278:E278"/>
     <mergeCell ref="B60:E60"/>
-    <mergeCell ref="A20:E20"/>
     <mergeCell ref="A43:B43"/>
-    <mergeCell ref="B171:E171"/>
     <mergeCell ref="A58:A59"/>
-    <mergeCell ref="A67:A68"/>
-    <mergeCell ref="B9:E9"/>
     <mergeCell ref="B187:E187"/>
-    <mergeCell ref="A15:E15"/>
     <mergeCell ref="A98:E98"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="A107:E107"/>
     <mergeCell ref="B241:E241"/>
     <mergeCell ref="B124:E124"/>
-    <mergeCell ref="B204:E204"/>
+    <mergeCell ref="B251:E251"/>
+    <mergeCell ref="B189:E189"/>
     <mergeCell ref="B216:E216"/>
-    <mergeCell ref="B198:E198"/>
-    <mergeCell ref="B251:E251"/>
     <mergeCell ref="B213:E213"/>
     <mergeCell ref="A162:E162"/>
-    <mergeCell ref="B189:E189"/>
-    <mergeCell ref="B296:E296"/>
     <mergeCell ref="B305:E305"/>
     <mergeCell ref="B188:E188"/>
     <mergeCell ref="B126:E126"/>
-    <mergeCell ref="B75:E75"/>
-    <mergeCell ref="B135:E135"/>
-    <mergeCell ref="B233:E233"/>
     <mergeCell ref="B218:E218"/>
-    <mergeCell ref="B62:E62"/>
-    <mergeCell ref="B227:E227"/>
     <mergeCell ref="A335:E335"/>
     <mergeCell ref="B59:E59"/>
     <mergeCell ref="B190:E190"/>
-    <mergeCell ref="B202:E202"/>
-    <mergeCell ref="B199:E199"/>
     <mergeCell ref="B282:E282"/>
-    <mergeCell ref="B70:E70"/>
-    <mergeCell ref="A47:B47"/>
     <mergeCell ref="B219:E219"/>
-    <mergeCell ref="B293:E293"/>
-    <mergeCell ref="B322:E322"/>
     <mergeCell ref="A109:E109"/>
     <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A333:E333"/>
     <mergeCell ref="B73:E73"/>
-    <mergeCell ref="B88:E88"/>
-    <mergeCell ref="A10:E10"/>
-    <mergeCell ref="B82:E82"/>
     <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A344:E344"/>
-    <mergeCell ref="B128:E128"/>
+    <mergeCell ref="B137:E137"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.236111111111111" right="0.236111111111111" top="0.747916666666667" bottom="0.747222222222222" header="0.511811023622047" footer="0.314583333333333"/>
